--- a/output/StructureDefinition-t-cabs-patient.xlsx
+++ b/output/StructureDefinition-t-cabs-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-patient.xlsx
+++ b/output/StructureDefinition-t-cabs-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-patient.xlsx
+++ b/output/StructureDefinition-t-cabs-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-patient.xlsx
+++ b/output/StructureDefinition-t-cabs-patient.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-patient</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
